--- a/output_image/典型日2_09-25_逐时数据.xlsx
+++ b/output_image/典型日2_09-25_逐时数据.xlsx
@@ -1293,13 +1293,13 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>103.287633895874</v>
+        <v>81.15168476104736</v>
       </c>
       <c r="S5">
         <v>0.03573171049356461</v>
       </c>
       <c r="T5">
-        <v>103.2519021853805</v>
+        <v>81.1159530505538</v>
       </c>
       <c r="U5">
         <v>0.3</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>11.23763084411621</v>
+        <v>-10.89831829071045</v>
       </c>
       <c r="Y5">
         <v>97.05000305175781</v>
@@ -1409,13 +1409,13 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>96.11762805651593</v>
+        <v>78.43303565979004</v>
       </c>
       <c r="S6">
         <v>0.03606293350458145</v>
       </c>
       <c r="T6">
-        <v>96.08156512301134</v>
+        <v>78.39697272628545</v>
       </c>
       <c r="U6">
         <v>0.3</v>
@@ -1427,16 +1427,16 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>11.23763080309796</v>
+        <v>-6.446961593627929</v>
       </c>
       <c r="Y6">
-        <v>101.2384624481201</v>
+        <v>78.17025470733643</v>
       </c>
       <c r="Z6">
         <v>0.0354127325117588</v>
       </c>
       <c r="AA6">
-        <v>101.2030497156084</v>
+        <v>78.13484197482467</v>
       </c>
       <c r="AB6">
         <v>0.3</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>11.35846519470215</v>
+        <v>-11.70974254608154</v>
       </c>
       <c r="AF6">
         <v>35.71780967712402</v>
@@ -1525,13 +1525,13 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <v>92.72762863369621</v>
+        <v>78.62881397247315</v>
       </c>
       <c r="S7">
         <v>0.03567740321159363</v>
       </c>
       <c r="T7">
-        <v>92.69195123048462</v>
+        <v>78.59313656926156</v>
       </c>
       <c r="U7">
         <v>0.3</v>
@@ -1543,16 +1543,16 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>11.23763076992668</v>
+        <v>-2.861183891296386</v>
       </c>
       <c r="Y7">
-        <v>97.84846305847168</v>
+        <v>74.78025531768799</v>
       </c>
       <c r="Z7">
         <v>0.038016177713871</v>
       </c>
       <c r="AA7">
-        <v>97.81044688075781</v>
+        <v>74.74223913997412</v>
       </c>
       <c r="AB7">
         <v>0.3</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>11.35846519470215</v>
+        <v>-11.70974254608154</v>
       </c>
       <c r="AF7">
         <v>35.08097267150879</v>
@@ -1641,13 +1641,13 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>82.46763412686028</v>
+        <v>68.3688194656372</v>
       </c>
       <c r="S8">
         <v>0.03458746522665024</v>
       </c>
       <c r="T8">
-        <v>82.43304666163363</v>
+        <v>68.33423200041055</v>
       </c>
       <c r="U8">
         <v>0.3</v>
@@ -1659,16 +1659,16 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>11.23763076992668</v>
+        <v>-2.861183891296386</v>
       </c>
       <c r="Y8">
-        <v>87.58846855163574</v>
+        <v>64.52026081085205</v>
       </c>
       <c r="Z8">
         <v>0.03413240239024162</v>
       </c>
       <c r="AA8">
-        <v>87.5543361492455</v>
+        <v>64.48612840846181</v>
       </c>
       <c r="AB8">
         <v>0.3</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>11.35846519470215</v>
+        <v>-11.70974254608154</v>
       </c>
       <c r="AF8">
         <v>41.10579490661621</v>
@@ -1757,13 +1757,13 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>84.0576304647509</v>
+        <v>69.95881580352783</v>
       </c>
       <c r="S9">
         <v>0.03484964743256569</v>
       </c>
       <c r="T9">
-        <v>84.02278081731833</v>
+        <v>69.92396615609526</v>
       </c>
       <c r="U9">
         <v>0.3</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>11.23763076992668</v>
+        <v>-2.861183891296386</v>
       </c>
       <c r="Y9">
-        <v>89.17846493721008</v>
+        <v>75.11025714874268</v>
       </c>
       <c r="Z9">
         <v>0.03577825427055359</v>
       </c>
       <c r="AA9">
-        <v>89.14268668293953</v>
+        <v>75.07447889447212</v>
       </c>
       <c r="AB9">
         <v>0.3</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF9">
         <v>36.5798397064209</v>
@@ -1873,13 +1873,13 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <v>75.59763135284672</v>
+        <v>64.44484519195557</v>
       </c>
       <c r="S10">
         <v>0.03512931615114212</v>
       </c>
       <c r="T10">
-        <v>75.56250203669558</v>
+        <v>64.40971587580442</v>
       </c>
       <c r="U10">
         <v>0.3</v>
@@ -1891,16 +1891,16 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y10">
-        <v>80.71846585273742</v>
+        <v>66.65025806427002</v>
       </c>
       <c r="Z10">
         <v>0.0365709587931633</v>
       </c>
       <c r="AA10">
-        <v>80.68189489394426</v>
+        <v>66.61368710547686</v>
       </c>
       <c r="AB10">
         <v>0.3</v>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF10">
         <v>40.69404220581055</v>
@@ -1989,13 +1989,13 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>69.95763196319828</v>
+        <v>58.80484580230713</v>
       </c>
       <c r="S11">
         <v>0.03767980635166168</v>
       </c>
       <c r="T11">
-        <v>69.91995215684662</v>
+        <v>58.76716599595547</v>
       </c>
       <c r="U11">
         <v>0.3</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y11">
-        <v>84.07846646308899</v>
+        <v>70.01025867462158</v>
       </c>
       <c r="Z11">
         <v>0.03776922821998596</v>
       </c>
       <c r="AA11">
-        <v>84.040697234869</v>
+        <v>69.9724894464016</v>
       </c>
       <c r="AB11">
         <v>0.3</v>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF11">
         <v>38.20641326904297</v>
@@ -2105,13 +2105,13 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>73.19762982696781</v>
+        <v>62.04484366607666</v>
       </c>
       <c r="S12">
         <v>0.03487350046634674</v>
       </c>
       <c r="T12">
-        <v>73.16275632650147</v>
+        <v>62.00997016561031</v>
       </c>
       <c r="U12">
         <v>0.3</v>
@@ -2123,16 +2123,16 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y12">
-        <v>87.31846432685852</v>
+        <v>73.25025653839111</v>
       </c>
       <c r="Z12">
         <v>0.03638514876365662</v>
       </c>
       <c r="AA12">
-        <v>87.28207917809486</v>
+        <v>73.21387138962746</v>
       </c>
       <c r="AB12">
         <v>0.3</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF12">
         <v>39.28854370117188</v>
@@ -2221,13 +2221,13 @@
         <v>0</v>
       </c>
       <c r="R13">
-        <v>65.15762891144047</v>
+        <v>54.00484275054932</v>
       </c>
       <c r="S13">
         <v>0.03630546480417252</v>
       </c>
       <c r="T13">
-        <v>65.1213234466363</v>
+        <v>53.96853728574514</v>
       </c>
       <c r="U13">
         <v>0.4125</v>
@@ -2239,16 +2239,16 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y13">
-        <v>70.27846341133117</v>
+        <v>56.21025562286377</v>
       </c>
       <c r="Z13">
         <v>0.03639162704348564</v>
       </c>
       <c r="AA13">
-        <v>70.24207178428769</v>
+        <v>56.17386399582028</v>
       </c>
       <c r="AB13">
         <v>0.3</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF13">
         <v>35.68571853637695</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="R14">
-        <v>65.60763348907719</v>
+        <v>54.45484732818603</v>
       </c>
       <c r="S14">
         <v>0.03466896712779999</v>
       </c>
       <c r="T14">
-        <v>65.57296452194939</v>
+        <v>54.42017836105823</v>
       </c>
       <c r="U14">
         <v>0.4125</v>
@@ -2355,16 +2355,16 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y14">
-        <v>70.72846798896789</v>
+        <v>56.66026020050049</v>
       </c>
       <c r="Z14">
         <v>0.03580131754279137</v>
       </c>
       <c r="AA14">
-        <v>70.6926666714251</v>
+        <v>56.6244588829577</v>
       </c>
       <c r="AB14">
         <v>0.3</v>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="AE14">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF14">
         <v>34.26508712768555</v>
@@ -2453,13 +2453,13 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>56.39763058990726</v>
+        <v>45.24484442901611</v>
       </c>
       <c r="S15">
         <v>0.03712150827050209</v>
       </c>
       <c r="T15">
-        <v>56.36050908163676</v>
+        <v>45.20772292074561</v>
       </c>
       <c r="U15">
         <v>0.4125</v>
@@ -2471,16 +2471,16 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y15">
-        <v>61.51846508979797</v>
+        <v>47.45025730133057</v>
       </c>
       <c r="Z15">
         <v>0.03625356405973434</v>
       </c>
       <c r="AA15">
-        <v>61.48221152573824</v>
+        <v>47.41400373727083</v>
       </c>
       <c r="AB15">
         <v>0.3</v>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF15">
         <v>37.89765167236328</v>
@@ -2569,13 +2569,13 @@
         <v>0</v>
       </c>
       <c r="R16">
-        <v>66.86762799591313</v>
+        <v>55.71484183502197</v>
       </c>
       <c r="S16">
         <v>0.03743930160999298</v>
       </c>
       <c r="T16">
-        <v>66.83018869430313</v>
+        <v>55.67740253341198</v>
       </c>
       <c r="U16">
         <v>0.4125</v>
@@ -2587,16 +2587,16 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y16">
-        <v>71.98846249580383</v>
+        <v>57.92025470733643</v>
       </c>
       <c r="Z16">
         <v>0.03720627352595329</v>
       </c>
       <c r="AA16">
-        <v>71.95125622227788</v>
+        <v>57.88304843381047</v>
       </c>
       <c r="AB16">
         <v>0.3</v>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF16">
         <v>37.53631401062012</v>
@@ -2685,13 +2685,13 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>59.57763089508304</v>
+        <v>48.42484473419189</v>
       </c>
       <c r="S17">
         <v>0.03410051017999649</v>
       </c>
       <c r="T17">
-        <v>59.54353038490304</v>
+        <v>48.3907442240119</v>
       </c>
       <c r="U17">
         <v>0.4125</v>
@@ -2703,16 +2703,16 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y17">
-        <v>73.69846539497375</v>
+        <v>59.63025760650635</v>
       </c>
       <c r="Z17">
         <v>0.03550795093178749</v>
       </c>
       <c r="AA17">
-        <v>73.66295744404196</v>
+        <v>59.59474965557456</v>
       </c>
       <c r="AB17">
         <v>0.3</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="AE17">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF17">
         <v>37.14128684997559</v>
@@ -2801,13 +2801,13 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>62.24763287872562</v>
+        <v>51.09484671783447</v>
       </c>
       <c r="S18">
         <v>0.03643597662448883</v>
       </c>
       <c r="T18">
-        <v>62.21119690210113</v>
+        <v>51.05841074120998</v>
       </c>
       <c r="U18">
         <v>0.4125</v>
@@ -2819,16 +2819,16 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y18">
-        <v>76.36846737861633</v>
+        <v>62.30025959014893</v>
       </c>
       <c r="Z18">
         <v>0.03603518009185791</v>
       </c>
       <c r="AA18">
-        <v>76.33243219852447</v>
+        <v>62.26422441005707</v>
       </c>
       <c r="AB18">
         <v>0.3</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF18">
         <v>40.83829116821289</v>
@@ -2917,13 +2917,13 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>65.36762799591313</v>
+        <v>54.21484183502197</v>
       </c>
       <c r="S19">
         <v>0.0366675853729248</v>
       </c>
       <c r="T19">
-        <v>65.3309604105402</v>
+        <v>54.17817424964905</v>
       </c>
       <c r="U19">
         <v>0.4125</v>
@@ -2935,16 +2935,16 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y19">
-        <v>70.48846249580383</v>
+        <v>56.42025470733643</v>
       </c>
       <c r="Z19">
         <v>0.03762737661600113</v>
       </c>
       <c r="AA19">
-        <v>70.45083511918783</v>
+        <v>56.38262733072042</v>
       </c>
       <c r="AB19">
         <v>0.3</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="AE19">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF19">
         <v>41.15850639343261</v>
@@ -3033,13 +3033,13 @@
         <v>0</v>
       </c>
       <c r="R20">
-        <v>48.77763165802249</v>
+        <v>37.62484549713135</v>
       </c>
       <c r="S20">
         <v>0.03591757267713547</v>
       </c>
       <c r="T20">
-        <v>48.74171408534536</v>
+        <v>37.58892792445421</v>
       </c>
       <c r="U20">
         <v>0.4125</v>
@@ -3051,16 +3051,16 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y20">
-        <v>53.89846615791321</v>
+        <v>39.8302583694458</v>
       </c>
       <c r="Z20">
         <v>0.03651294112205505</v>
       </c>
       <c r="AA20">
-        <v>53.86195321679115</v>
+        <v>39.79374542832375</v>
       </c>
       <c r="AB20">
         <v>0.3</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="AE20">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF20">
         <v>43.4929895401001</v>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="R21">
-        <v>48.98763074249515</v>
+        <v>37.834844581604</v>
       </c>
       <c r="S21">
         <v>0.03704589605331421</v>
       </c>
       <c r="T21">
-        <v>48.95058484644183</v>
+        <v>37.79779868555069</v>
       </c>
       <c r="U21">
         <v>0.4125</v>
@@ -3167,16 +3167,16 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>11.23763074249515</v>
+        <v>0.08484458160400443</v>
       </c>
       <c r="Y21">
-        <v>54.10846524238586</v>
+        <v>40.04025745391846</v>
       </c>
       <c r="Z21">
         <v>0.03573377430438995</v>
       </c>
       <c r="AA21">
-        <v>54.07273146808147</v>
+        <v>40.00452367961407</v>
       </c>
       <c r="AB21">
         <v>0.3</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="AE21">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF21">
         <v>40.45937728881836</v>
@@ -3265,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="R22">
-        <v>55.4076288860752</v>
+        <v>46.97896252330433</v>
       </c>
       <c r="S22">
         <v>0.04309110715985298</v>
       </c>
       <c r="T22">
-        <v>55.36453777891535</v>
+        <v>46.93587141614448</v>
       </c>
       <c r="U22">
         <v>0.4125</v>
@@ -3283,16 +3283,16 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>11.23763071712989</v>
+        <v>2.80896435435902</v>
       </c>
       <c r="Y22">
-        <v>60.52846341133117</v>
+        <v>46.46025562286377</v>
       </c>
       <c r="Z22">
         <v>0.04367770999670029</v>
       </c>
       <c r="AA22">
-        <v>60.48478570133447</v>
+        <v>46.41657791286707</v>
       </c>
       <c r="AB22">
         <v>0.3</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>11.35846524238586</v>
+        <v>-2.709742546081543</v>
       </c>
       <c r="AF22">
         <v>42.60240173339844</v>
@@ -3381,13 +3381,13 @@
         <v>0</v>
       </c>
       <c r="R23">
-        <v>62.30763041195411</v>
+        <v>53.87896404918324</v>
       </c>
       <c r="S23">
         <v>0.07629504799842834</v>
       </c>
       <c r="T23">
-        <v>62.23133536395568</v>
+        <v>53.80266900118481</v>
       </c>
       <c r="U23">
         <v>0.4125</v>
@@ -3399,16 +3399,16 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>11.23763071712989</v>
+        <v>2.80896435435902</v>
       </c>
       <c r="Y23">
-        <v>67.42846497956076</v>
+        <v>61.66471576690674</v>
       </c>
       <c r="Z23">
         <v>0.07860137522220612</v>
       </c>
       <c r="AA23">
-        <v>67.34986360433855</v>
+        <v>61.58611439168453</v>
       </c>
       <c r="AB23">
         <v>0.3</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>11.35846528473653</v>
+        <v>5.59471607208252</v>
       </c>
       <c r="AF23">
         <v>43.43716716766357</v>
@@ -3497,13 +3497,13 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>57.20763193783301</v>
+        <v>48.77896557506214</v>
       </c>
       <c r="S24">
         <v>0.8095256090164185</v>
       </c>
       <c r="T24">
-        <v>56.3981063288166</v>
+        <v>47.96943996604573</v>
       </c>
       <c r="U24">
         <v>0.4125</v>
@@ -3515,16 +3515,16 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>11.23763071712989</v>
+        <v>2.80896435435902</v>
       </c>
       <c r="Y24">
-        <v>62.32846650543966</v>
+        <v>56.56471729278564</v>
       </c>
       <c r="Z24">
         <v>0.8222606182098389</v>
       </c>
       <c r="AA24">
-        <v>61.50620588722982</v>
+        <v>55.74245667457581</v>
       </c>
       <c r="AB24">
         <v>0.3</v>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>11.35846528473653</v>
+        <v>5.59471607208252</v>
       </c>
       <c r="AF24">
         <v>43.42883217187067</v>
@@ -3613,13 +3613,13 @@
         <v>0</v>
       </c>
       <c r="R25">
-        <v>56.21763025936622</v>
+        <v>47.78896389659535</v>
       </c>
       <c r="S25">
         <v>2.442182779312134</v>
       </c>
       <c r="T25">
-        <v>53.77544748005408</v>
+        <v>45.34678111728321</v>
       </c>
       <c r="U25">
         <v>0.4125</v>
@@ -3631,16 +3631,16 @@
         <v>0</v>
       </c>
       <c r="X25">
-        <v>11.23763071712989</v>
+        <v>2.80896435435902</v>
       </c>
       <c r="Y25">
-        <v>61.33846482697286</v>
+        <v>55.57471561431885</v>
       </c>
       <c r="Z25">
         <v>2.440153837203979</v>
       </c>
       <c r="AA25">
-        <v>58.89831098976888</v>
+        <v>53.13456177711487</v>
       </c>
       <c r="AB25">
         <v>0.3</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>11.35846528473653</v>
+        <v>5.59471607208252</v>
       </c>
       <c r="AF25">
         <v>46.89986130236635</v>
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>58.07763086971778</v>
+        <v>49.64896450694691</v>
       </c>
       <c r="S26">
         <v>2.568434476852417</v>
       </c>
       <c r="T26">
-        <v>55.50919639286536</v>
+        <v>47.08053003009449</v>
       </c>
       <c r="U26">
         <v>0.4125</v>
@@ -3747,16 +3747,16 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>11.23763071712989</v>
+        <v>2.80896435435902</v>
       </c>
       <c r="Y26">
-        <v>63.19846547039275</v>
+        <v>59.59615067259906</v>
       </c>
       <c r="Z26">
         <v>2.568632841110229</v>
       </c>
       <c r="AA26">
-        <v>60.62983262928253</v>
+        <v>57.02751783148883</v>
       </c>
       <c r="AB26">
         <v>0.3</v>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>11.35846531780486</v>
+        <v>7.75615052001117</v>
       </c>
       <c r="AF26">
         <v>46.62751714768047</v>
@@ -3845,13 +3845,13 @@
         <v>0</v>
       </c>
       <c r="R27">
-        <v>56.81763252648319</v>
+        <v>50.719601990993</v>
       </c>
       <c r="S27">
         <v>2.728293418884277</v>
       </c>
       <c r="T27">
-        <v>54.08933910759891</v>
+        <v>47.99130857210872</v>
       </c>
       <c r="U27">
         <v>0.4125</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>11.2376306954285</v>
+        <v>5.139600159938311</v>
       </c>
       <c r="Y27">
-        <v>61.93846714885955</v>
+        <v>58.33615235106586</v>
       </c>
       <c r="Z27">
         <v>2.730469942092896</v>
       </c>
       <c r="AA27">
-        <v>59.20799720676666</v>
+        <v>55.60568240897296</v>
       </c>
       <c r="AB27">
         <v>0.3</v>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>11.35846531780486</v>
+        <v>7.75615052001117</v>
       </c>
       <c r="AF27">
         <v>63.38188562977303</v>
@@ -3961,13 +3961,13 @@
         <v>0</v>
       </c>
       <c r="R28">
-        <v>70.37763008507693</v>
+        <v>64.27959954958675</v>
       </c>
       <c r="S28">
         <v>6.130349636077881</v>
       </c>
       <c r="T28">
-        <v>64.24728044899905</v>
+        <v>58.14924991350887</v>
       </c>
       <c r="U28">
         <v>0.4125</v>
@@ -3979,16 +3979,16 @@
         <v>0.2260699272155762</v>
       </c>
       <c r="X28">
-        <v>11.2376306954285</v>
+        <v>5.139600159938311</v>
       </c>
       <c r="Y28">
-        <v>75.49846470745331</v>
+        <v>71.89614990965961</v>
       </c>
       <c r="Z28">
         <v>6.138359069824219</v>
       </c>
       <c r="AA28">
-        <v>69.36010563762909</v>
+        <v>65.75779083983539</v>
       </c>
       <c r="AB28">
         <v>0.3</v>
@@ -4000,7 +4000,7 @@
         <v>0.227671816945076</v>
       </c>
       <c r="AE28">
-        <v>11.35846531780486</v>
+        <v>7.75615052001117</v>
       </c>
       <c r="AF28">
         <v>55.35234936376541</v>
@@ -4077,13 +4077,13 @@
         <v>0</v>
       </c>
       <c r="R29">
-        <v>74.03763372932917</v>
+        <v>69.87252464652569</v>
       </c>
       <c r="S29">
         <v>11.74884414672852</v>
       </c>
       <c r="T29">
-        <v>62.28878958260066</v>
+        <v>58.12368049979717</v>
       </c>
       <c r="U29">
         <v>0.4125</v>
@@ -4095,16 +4095,16 @@
         <v>1</v>
       </c>
       <c r="X29">
-        <v>11.23763067757136</v>
+        <v>7.072521594767879</v>
       </c>
       <c r="Y29">
-        <v>79.15846836956268</v>
+        <v>75.55615357176899</v>
       </c>
       <c r="Z29">
         <v>11.74545383453369</v>
       </c>
       <c r="AA29">
-        <v>67.41301453502899</v>
+        <v>63.8106997372353</v>
       </c>
       <c r="AB29">
         <v>0.3</v>
@@ -4116,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="AE29">
-        <v>11.35846531780486</v>
+        <v>7.75615052001117</v>
       </c>
       <c r="AF29">
         <v>74.62680032010921</v>
@@ -4193,13 +4193,13 @@
         <v>0</v>
       </c>
       <c r="R30">
-        <v>88.99763281380183</v>
+        <v>84.83252373099835</v>
       </c>
       <c r="S30">
         <v>20.91296195983887</v>
       </c>
       <c r="T30">
-        <v>68.08467085396296</v>
+        <v>63.91956177115948</v>
       </c>
       <c r="U30">
         <v>0.4125</v>
@@ -4211,16 +4211,16 @@
         <v>1</v>
       </c>
       <c r="X30">
-        <v>11.23763067757136</v>
+        <v>7.072521594767879</v>
       </c>
       <c r="Y30">
-        <v>89.11846745403534</v>
+        <v>85.51615265624164</v>
       </c>
       <c r="Z30">
         <v>20.91768836975098</v>
       </c>
       <c r="AA30">
-        <v>68.20077908428436</v>
+        <v>64.59846428649067</v>
       </c>
       <c r="AB30">
         <v>0.3</v>
@@ -4232,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="AE30">
-        <v>11.35846531780486</v>
+        <v>7.75615052001117</v>
       </c>
       <c r="AF30">
         <v>75.4130077716359</v>
@@ -4309,13 +4309,13 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>99.33762915169245</v>
+        <v>95.17252006888897</v>
       </c>
       <c r="S31">
         <v>30.91916084289551</v>
       </c>
       <c r="T31">
-        <v>68.41846830879695</v>
+        <v>64.25335922599346</v>
       </c>
       <c r="U31">
         <v>0.4125</v>
@@ -4327,16 +4327,16 @@
         <v>1</v>
       </c>
       <c r="X31">
-        <v>11.23763067757136</v>
+        <v>7.072521594767879</v>
       </c>
       <c r="Y31">
-        <v>94.45846379192596</v>
+        <v>90.85614899413227</v>
       </c>
       <c r="Z31">
         <v>30.91762924194336</v>
       </c>
       <c r="AA31">
-        <v>63.54083454998261</v>
+        <v>59.93851975218891</v>
       </c>
       <c r="AB31">
         <v>0.3</v>
@@ -4348,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="AE31">
-        <v>11.35846531780486</v>
+        <v>7.75615052001117</v>
       </c>
       <c r="AF31">
         <v>92.35036907171617</v>
@@ -4425,13 +4425,13 @@
         <v>20.82362365722656</v>
       </c>
       <c r="R32">
-        <v>97.66582015510892</v>
+        <v>89.75691737280867</v>
       </c>
       <c r="S32">
         <v>42.21054840087891</v>
       </c>
       <c r="T32">
-        <v>55.45527175423001</v>
+        <v>47.54636897192977</v>
       </c>
       <c r="U32">
         <v>0.4125</v>
@@ -4443,16 +4443,16 @@
         <v>1</v>
       </c>
       <c r="X32">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y32">
-        <v>101.7390360077002</v>
+        <v>99.95089353222949</v>
       </c>
       <c r="Z32">
         <v>42.21054077148438</v>
       </c>
       <c r="AA32">
-        <v>59.52849523621587</v>
+        <v>57.74035276074511</v>
       </c>
       <c r="AB32">
         <v>0.3</v>
@@ -4464,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="AE32">
-        <v>11.70903722840337</v>
+        <v>9.920894752932604</v>
       </c>
       <c r="AF32">
         <v>102.7687940299486</v>
@@ -4541,13 +4541,13 @@
         <v>21.40749197873202</v>
       </c>
       <c r="R33">
-        <v>103.7254881760902</v>
+        <v>95.81658539378991</v>
       </c>
       <c r="S33">
         <v>52.18913269042969</v>
       </c>
       <c r="T33">
-        <v>51.53635548566047</v>
+        <v>43.62745270336022</v>
       </c>
       <c r="U33">
         <v>0.4125</v>
@@ -4559,16 +4559,16 @@
         <v>1</v>
       </c>
       <c r="X33">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y33">
-        <v>102.7590402801612</v>
+        <v>100.9708978046904</v>
       </c>
       <c r="Z33">
         <v>52.19511795043945</v>
       </c>
       <c r="AA33">
-        <v>50.56392232972173</v>
+        <v>48.77577985425097</v>
       </c>
       <c r="AB33">
         <v>0.3</v>
@@ -4580,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="AE33">
-        <v>11.70903722840337</v>
+        <v>9.920894752932604</v>
       </c>
       <c r="AF33">
         <v>120.9566988355905</v>
@@ -4657,13 +4657,13 @@
         <v>21.68403181723615</v>
       </c>
       <c r="R34">
-        <v>109.8104476086863</v>
+        <v>101.9015448263861</v>
       </c>
       <c r="S34">
         <v>66.44149780273438</v>
       </c>
       <c r="T34">
-        <v>43.36894980595196</v>
+        <v>35.4600470236517</v>
       </c>
       <c r="U34">
         <v>0.4125</v>
@@ -4675,16 +4675,16 @@
         <v>1</v>
       </c>
       <c r="X34">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y34">
-        <v>119.9690393646338</v>
+        <v>118.1808968891631</v>
       </c>
       <c r="Z34">
         <v>66.44684600830078</v>
       </c>
       <c r="AA34">
-        <v>53.52219335633306</v>
+        <v>51.7340508808623</v>
       </c>
       <c r="AB34">
         <v>0.3</v>
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="AE34">
-        <v>11.70903722840337</v>
+        <v>9.920894752932604</v>
       </c>
       <c r="AF34">
         <v>105.5135994234604</v>
@@ -4773,13 +4773,13 @@
         <v>21.80567017804842</v>
       </c>
       <c r="R35">
-        <v>136.8791733608455</v>
+        <v>128.9702705785453</v>
       </c>
       <c r="S35">
         <v>81.44853973388672</v>
       </c>
       <c r="T35">
-        <v>55.43063362695881</v>
+        <v>47.52173084465855</v>
       </c>
       <c r="U35">
         <v>0.4125</v>
@@ -4791,16 +4791,16 @@
         <v>1</v>
       </c>
       <c r="X35">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y35">
-        <v>149.9969553231278</v>
+        <v>149.8058120556513</v>
       </c>
       <c r="Z35">
         <v>81.44911956787109</v>
       </c>
       <c r="AA35">
-        <v>68.54783575525667</v>
+        <v>68.35669248778021</v>
       </c>
       <c r="AB35">
         <v>0.3</v>
@@ -4812,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="AE35">
-        <v>14.58695166101838</v>
+        <v>14.39580839354191</v>
       </c>
       <c r="AF35">
         <v>128.2639219409321</v>
@@ -4889,13 +4889,13 @@
         <v>21.84899192969697</v>
       </c>
       <c r="R36">
-        <v>139.3163419716973</v>
+        <v>131.407439189397</v>
       </c>
       <c r="S36">
         <v>95.79606628417969</v>
       </c>
       <c r="T36">
-        <v>43.52027568751757</v>
+        <v>35.61137290521731</v>
       </c>
       <c r="U36">
         <v>0.4125</v>
@@ -4907,16 +4907,16 @@
         <v>1</v>
       </c>
       <c r="X36">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y36">
-        <v>155.8655146775857</v>
+        <v>156.3239432252662</v>
       </c>
       <c r="Z36">
         <v>95.79791259765625</v>
       </c>
       <c r="AA36">
-        <v>60.06760207992946</v>
+        <v>60.52603062760994</v>
       </c>
       <c r="AB36">
         <v>0.3</v>
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="AE36">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF36">
         <v>112.5386520895619</v>
@@ -5005,13 +5005,13 @@
         <v>22.00036066273123</v>
       </c>
       <c r="R37">
-        <v>148.4019940213723</v>
+        <v>140.4930912390721</v>
       </c>
       <c r="S37">
         <v>106.8972244262695</v>
       </c>
       <c r="T37">
-        <v>41.5047695951028</v>
+        <v>33.59586681280254</v>
       </c>
       <c r="U37">
         <v>0.4125</v>
@@ -5023,16 +5023,16 @@
         <v>1</v>
       </c>
       <c r="X37">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y37">
-        <v>161.1010259360072</v>
+        <v>161.5594544836877</v>
       </c>
       <c r="Z37">
         <v>106.8978729248047</v>
       </c>
       <c r="AA37">
-        <v>54.20315301120255</v>
+        <v>54.66158155888306</v>
       </c>
       <c r="AB37">
         <v>0.3</v>
@@ -5044,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="AE37">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF37">
         <v>112.6659924398588</v>
@@ -5121,13 +5121,13 @@
         <v>22.24771287664013</v>
       </c>
       <c r="R38">
-        <v>119.0996825121122</v>
+        <v>111.190779729812</v>
       </c>
       <c r="S38">
         <v>116.560661315918</v>
       </c>
       <c r="T38">
-        <v>2.539021196194227</v>
+        <v>0</v>
       </c>
       <c r="U38">
         <v>0.4125</v>
@@ -5136,19 +5136,19 @@
         <v>0.55</v>
       </c>
       <c r="W38">
-        <v>1</v>
+        <v>0.9539305840797191</v>
       </c>
       <c r="X38">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y38">
-        <v>120.7921228566424</v>
+        <v>121.2505514043229</v>
       </c>
       <c r="Z38">
         <v>116.5629959106445</v>
       </c>
       <c r="AA38">
-        <v>4.229126945997848</v>
+        <v>4.68755549367836</v>
       </c>
       <c r="AB38">
         <v>0.3</v>
@@ -5160,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="AE38">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF38">
         <v>112.744541363878</v>
@@ -5237,13 +5237,13 @@
         <v>22.51692684597747</v>
       </c>
       <c r="R39">
-        <v>128.505172447475</v>
+        <v>120.5962696651747</v>
       </c>
       <c r="S39">
         <v>126.1924209594727</v>
       </c>
       <c r="T39">
-        <v>2.312751488002306</v>
+        <v>0</v>
       </c>
       <c r="U39">
         <v>0.4125</v>
@@ -5252,19 +5252,19 @@
         <v>0.55</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>0.9556538241223284</v>
       </c>
       <c r="X39">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y39">
-        <v>130.1933282714371</v>
+        <v>130.6517568191176</v>
       </c>
       <c r="Z39">
         <v>126.1920623779297</v>
       </c>
       <c r="AA39">
-        <v>4.001265893507366</v>
+        <v>4.459694441187878</v>
       </c>
       <c r="AB39">
         <v>0.3</v>
@@ -5276,7 +5276,7 @@
         <v>1</v>
       </c>
       <c r="AE39">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF39">
         <v>139.3603589972092</v>
@@ -5353,7 +5353,7 @@
         <v>22.79526417373745</v>
       </c>
       <c r="R40">
-        <v>129.1857445370526</v>
+        <v>121.2768417547523</v>
       </c>
       <c r="S40">
         <v>136.5410614013672</v>
@@ -5368,13 +5368,13 @@
         <v>0.55</v>
       </c>
       <c r="W40">
-        <v>0.9461310994009823</v>
+        <v>0.8882078439265593</v>
       </c>
       <c r="X40">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y40">
-        <v>130.8711154226454</v>
+        <v>131.3295439703259</v>
       </c>
       <c r="Z40">
         <v>136.5408325195312</v>
@@ -5389,10 +5389,10 @@
         <v>0.55</v>
       </c>
       <c r="AD40">
-        <v>0.9584760324639527</v>
+        <v>0.961833479018374</v>
       </c>
       <c r="AE40">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF40">
         <v>117.2681905441232</v>
@@ -5469,7 +5469,7 @@
         <v>23.08865757943684</v>
       </c>
       <c r="R41">
-        <v>125.4307903093323</v>
+        <v>117.5218875270321</v>
       </c>
       <c r="S41">
         <v>144.4848327636719</v>
@@ -5478,19 +5478,19 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>0.5766169606222841</v>
+        <v>0.633561060654846</v>
       </c>
       <c r="V41">
         <v>0.55</v>
       </c>
       <c r="W41">
-        <v>0.8681242723552479</v>
+        <v>0.8133856355653466</v>
       </c>
       <c r="X41">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y41">
-        <v>123.9931727374347</v>
+        <v>124.4516012851152</v>
       </c>
       <c r="Z41">
         <v>144.4916229248047</v>
@@ -5505,10 +5505,10 @@
         <v>0.55</v>
       </c>
       <c r="AD41">
-        <v>0.85813398886081</v>
+        <v>0.8613066886921288</v>
       </c>
       <c r="AE41">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF41">
         <v>119.7563148612558</v>
@@ -5585,7 +5585,7 @@
         <v>23.34659576802683</v>
       </c>
       <c r="R42">
-        <v>123.9095936083881</v>
+        <v>116.0006908260878</v>
       </c>
       <c r="S42">
         <v>151.8455963134766</v>
@@ -5594,19 +5594,19 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>0.7454795953462632</v>
+        <v>0.85</v>
       </c>
       <c r="V42">
         <v>0.55</v>
       </c>
       <c r="W42">
-        <v>0.8160236227897172</v>
+        <v>0.7639384588184633</v>
       </c>
       <c r="X42">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y42">
-        <v>122.4880117773261</v>
+        <v>122.9464403250066</v>
       </c>
       <c r="Z42">
         <v>151.8459014892578</v>
@@ -5621,10 +5621,10 @@
         <v>0.55</v>
       </c>
       <c r="AD42">
-        <v>0.8066599794660337</v>
+        <v>0.8096790174722254</v>
       </c>
       <c r="AE42">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF42">
         <v>126.5375784958545</v>
@@ -5701,7 +5701,7 @@
         <v>23.57512695739916</v>
       </c>
       <c r="R43">
-        <v>134.1258191097079</v>
+        <v>126.2169163274076</v>
       </c>
       <c r="S43">
         <v>157.3390350341797</v>
@@ -5716,13 +5716,13 @@
         <v>0.55</v>
       </c>
       <c r="W43">
-        <v>0.8524637200207243</v>
+        <v>0.8021970917769312</v>
       </c>
       <c r="X43">
-        <v>11.51822902379755</v>
+        <v>3.609326241497287</v>
       </c>
       <c r="Y43">
-        <v>132.7146605101891</v>
+        <v>133.1730890578696</v>
       </c>
       <c r="Z43">
         <v>157.3417358398438</v>
@@ -5737,10 +5737,10 @@
         <v>0.55</v>
       </c>
       <c r="AD43">
-        <v>0.8434803378887197</v>
+        <v>0.8463939230556403</v>
       </c>
       <c r="AE43">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF43">
         <v>117.5336864690973</v>
@@ -5817,7 +5817,7 @@
         <v>23.75500248256888</v>
       </c>
       <c r="R44">
-        <v>152.0643185297492</v>
+        <v>145.9019144780483</v>
       </c>
       <c r="S44">
         <v>161.7363739013672</v>
@@ -5832,13 +5832,13 @@
         <v>0.55</v>
       </c>
       <c r="W44">
-        <v>0.9401986384490336</v>
+        <v>0.9020971038155254</v>
       </c>
       <c r="X44">
-        <v>15.0498650448988</v>
+        <v>8.887460993197831</v>
       </c>
       <c r="Y44">
-        <v>146.9024748165549</v>
+        <v>147.3609033642354</v>
       </c>
       <c r="Z44">
         <v>161.7314147949219</v>
@@ -5847,16 +5847,16 @@
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0.3356542062895292</v>
+        <v>0.3323535207462296</v>
       </c>
       <c r="AC44">
         <v>0.55</v>
       </c>
       <c r="AD44">
-        <v>0.9083113197447118</v>
+        <v>0.9111458250154523</v>
       </c>
       <c r="AE44">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF44">
         <v>126.0605660999242</v>
@@ -5933,7 +5933,7 @@
         <v>23.89013378243082</v>
       </c>
       <c r="R45">
-        <v>138.7737946975591</v>
+        <v>134.0229357633583</v>
       </c>
       <c r="S45">
         <v>166.1117401123047</v>
@@ -5948,13 +5948,13 @@
         <v>0.55</v>
       </c>
       <c r="W45">
-        <v>0.8354243631650422</v>
+        <v>0.8068239828969836</v>
       </c>
       <c r="X45">
-        <v>17.86082772875909</v>
+        <v>13.10996879455826</v>
       </c>
       <c r="Y45">
-        <v>130.3110611499945</v>
+        <v>130.769489697675</v>
       </c>
       <c r="Z45">
         <v>166.1054534912109</v>
@@ -5963,16 +5963,16 @@
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>0.3356542062895292</v>
+        <v>0.3323535207462296</v>
       </c>
       <c r="AC45">
         <v>0.55</v>
       </c>
       <c r="AD45">
-        <v>0.7845080243370188</v>
+        <v>0.7872678888570888</v>
       </c>
       <c r="AE45">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF45">
         <v>124.8944060224696</v>
@@ -6049,7 +6049,7 @@
         <v>24.00089935986783</v>
       </c>
       <c r="R46">
-        <v>135.5752040046051</v>
+        <v>130.8243450704043</v>
       </c>
       <c r="S46">
         <v>168.7744903564453</v>
@@ -6064,13 +6064,13 @@
         <v>0.55</v>
       </c>
       <c r="W46">
-        <v>0.8032920361262855</v>
+        <v>0.775142883229025</v>
       </c>
       <c r="X46">
-        <v>17.86082772875909</v>
+        <v>13.10996879455826</v>
       </c>
       <c r="Y46">
-        <v>123.9920138225304</v>
+        <v>124.4504423702109</v>
       </c>
       <c r="Z46">
         <v>168.7755737304688</v>
@@ -6079,16 +6079,16 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC46">
         <v>0.55</v>
       </c>
       <c r="AD46">
-        <v>0.7346561536241211</v>
+        <v>0.7373723556049397</v>
       </c>
       <c r="AE46">
-        <v>17.83842774747593</v>
+        <v>18.29685629515644</v>
       </c>
       <c r="AF46">
         <v>122.0115459564822</v>
@@ -6165,7 +6165,7 @@
         <v>24.06853089008276</v>
       </c>
       <c r="R47">
-        <v>158.0752194178485</v>
+        <v>153.3243604836476</v>
       </c>
       <c r="S47">
         <v>171.9535827636719</v>
@@ -6180,13 +6180,13 @@
         <v>0.425</v>
       </c>
       <c r="W47">
-        <v>0.9192900600105702</v>
+        <v>0.8916613310370641</v>
       </c>
       <c r="X47">
-        <v>17.86082772875909</v>
+        <v>13.10996879455826</v>
       </c>
       <c r="Y47">
-        <v>149.3009591438625</v>
+        <v>150.1684324057458</v>
       </c>
       <c r="Z47">
         <v>171.9524078369141</v>
@@ -6195,16 +6195,16 @@
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC47">
         <v>0.425</v>
       </c>
       <c r="AD47">
-        <v>0.8682690810905361</v>
+        <v>0.8733139261892223</v>
       </c>
       <c r="AE47">
-        <v>20.355168959484</v>
+        <v>21.22264222136733</v>
       </c>
       <c r="AF47">
         <v>134.4425058229721</v>
@@ -6281,7 +6281,7 @@
         <v>24.12164793340473</v>
       </c>
       <c r="R48">
-        <v>157.718650711732</v>
+        <v>152.9677917775312</v>
       </c>
       <c r="S48">
         <v>166.9615173339844</v>
@@ -6296,13 +6296,13 @@
         <v>0.425</v>
       </c>
       <c r="W48">
-        <v>0.9446407365610889</v>
+        <v>0.9161859224814028</v>
       </c>
       <c r="X48">
-        <v>17.86082772875909</v>
+        <v>13.10996879455826</v>
       </c>
       <c r="Y48">
-        <v>146.1527402073235</v>
+        <v>147.0202134692068</v>
       </c>
       <c r="Z48">
         <v>166.9587860107422</v>
@@ -6311,16 +6311,16 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC48">
         <v>0.425</v>
       </c>
       <c r="AD48">
-        <v>0.8753821448960462</v>
+        <v>0.880577877822779</v>
       </c>
       <c r="AE48">
-        <v>20.355168959484</v>
+        <v>21.22264222136733</v>
       </c>
       <c r="AF48">
         <v>128.4806755960753</v>
@@ -6397,7 +6397,7 @@
         <v>24.0255547931837</v>
       </c>
       <c r="R49">
-        <v>161.0196553565074</v>
+        <v>156.2687964223066</v>
       </c>
       <c r="S49">
         <v>172.7519683837891</v>
@@ -6412,13 +6412,13 @@
         <v>0.425</v>
       </c>
       <c r="W49">
-        <v>0.9320857924975018</v>
+        <v>0.9045847516778325</v>
       </c>
       <c r="X49">
-        <v>17.86082772875909</v>
+        <v>13.10996879455826</v>
       </c>
       <c r="Y49">
-        <v>147.1873304539055</v>
+        <v>148.0548037157889</v>
       </c>
       <c r="Z49">
         <v>172.7433166503906</v>
@@ -6427,16 +6427,16 @@
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC49">
         <v>0.425</v>
       </c>
       <c r="AD49">
-        <v>0.8520580321598954</v>
+        <v>0.8570797793319668</v>
       </c>
       <c r="AE49">
-        <v>20.355168959484</v>
+        <v>21.22264222136733</v>
       </c>
       <c r="AF49">
         <v>143.4054979822918</v>
@@ -6513,7 +6513,7 @@
         <v>24.03888909241535</v>
       </c>
       <c r="R50">
-        <v>159.1233272031127</v>
+        <v>155.6395849601479</v>
       </c>
       <c r="S50">
         <v>174.4082336425781</v>
@@ -6528,13 +6528,13 @@
         <v>0.425</v>
       </c>
       <c r="W50">
-        <v>0.9123613253787695</v>
+        <v>0.8923866821511786</v>
       </c>
       <c r="X50">
-        <v>19.97171727861142</v>
+        <v>16.48797503564661</v>
       </c>
       <c r="Y50">
-        <v>142.3719222263665</v>
+        <v>143.2393954882498</v>
       </c>
       <c r="Z50">
         <v>174.4130706787109</v>
@@ -6543,16 +6543,16 @@
         <v>0</v>
       </c>
       <c r="AB50">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC50">
         <v>0.425</v>
       </c>
       <c r="AD50">
-        <v>0.8162915868193847</v>
+        <v>0.8212652579926956</v>
       </c>
       <c r="AE50">
-        <v>20.355168959484</v>
+        <v>21.22264222136733</v>
       </c>
       <c r="AF50">
         <v>151.3986918214749</v>
@@ -6629,7 +6629,7 @@
         <v>24.03458682360463</v>
       </c>
       <c r="R51">
-        <v>158.4403769658385</v>
+        <v>154.9566347228737</v>
       </c>
       <c r="S51">
         <v>163.1277313232422</v>
@@ -6644,13 +6644,13 @@
         <v>0.425</v>
       </c>
       <c r="W51">
-        <v>0.9712657417633328</v>
+        <v>0.949909825054961</v>
       </c>
       <c r="X51">
-        <v>19.97171727861142</v>
+        <v>16.48797503564661</v>
       </c>
       <c r="Y51">
-        <v>139.5365097263665</v>
+        <v>140.4039829882498</v>
       </c>
       <c r="Z51">
         <v>163.1290435791016</v>
@@ -6659,16 +6659,16 @@
         <v>0</v>
       </c>
       <c r="AB51">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC51">
         <v>0.425</v>
       </c>
       <c r="AD51">
-        <v>0.8553750249795645</v>
+        <v>0.8606927369139368</v>
       </c>
       <c r="AE51">
-        <v>20.355168959484</v>
+        <v>21.22264222136733</v>
       </c>
       <c r="AF51">
         <v>136.4040498775188</v>
@@ -6745,7 +6745,7 @@
         <v>23.7970557938239</v>
       </c>
       <c r="R52">
-        <v>152.8050040753661</v>
+        <v>149.3212618324013</v>
       </c>
       <c r="S52">
         <v>166.5715637207031</v>
@@ -6760,13 +6760,13 @@
         <v>0.425</v>
       </c>
       <c r="W52">
-        <v>0.9173534825642871</v>
+        <v>0.8964390949872687</v>
       </c>
       <c r="X52">
-        <v>19.97171727861142</v>
+        <v>16.48797503564661</v>
       </c>
       <c r="Y52">
-        <v>133.671090817675</v>
+        <v>134.5385640795584</v>
       </c>
       <c r="Z52">
         <v>166.5753631591797</v>
@@ -6775,16 +6775,16 @@
         <v>0</v>
       </c>
       <c r="AB52">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC52">
         <v>0.425</v>
       </c>
       <c r="AD52">
-        <v>0.8024661527523654</v>
+        <v>0.8076738452071877</v>
       </c>
       <c r="AE52">
-        <v>20.355168959484</v>
+        <v>21.22264222136733</v>
       </c>
       <c r="AF52">
         <v>133.5467017143781</v>
@@ -6861,7 +6861,7 @@
         <v>23.69554148994814</v>
       </c>
       <c r="R53">
-        <v>150.4754324699685</v>
+        <v>148.1300328208698</v>
       </c>
       <c r="S53">
         <v>166.0818634033203</v>
@@ -6876,13 +6876,13 @@
         <v>0.425</v>
       </c>
       <c r="W53">
-        <v>0.9060316965769317</v>
+        <v>0.8919097473102434</v>
       </c>
       <c r="X53">
-        <v>21.53577967761602</v>
+        <v>19.19038002851729</v>
       </c>
       <c r="Y53">
-        <v>130.9005121315285</v>
+        <v>132.4155225061502</v>
       </c>
       <c r="Z53">
         <v>166.0802764892578</v>
@@ -6891,16 +6891,16 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC53">
         <v>0.425</v>
       </c>
       <c r="AD53">
-        <v>0.7881761452871574</v>
+        <v>0.7972983023948355</v>
       </c>
       <c r="AE53">
-        <v>21.90197129140388</v>
+        <v>23.4169816660255</v>
       </c>
       <c r="AF53">
         <v>133.675550568387</v>
@@ -6977,7 +6977,7 @@
         <v>23.5924808490774</v>
       </c>
       <c r="R54">
-        <v>149.6185137797162</v>
+        <v>147.2731141306175</v>
       </c>
       <c r="S54">
         <v>163.5411682128906</v>
@@ -6992,13 +6992,13 @@
         <v>0.425</v>
       </c>
       <c r="W54">
-        <v>0.9148675860316069</v>
+        <v>0.9005262451036421</v>
       </c>
       <c r="X54">
-        <v>21.53577967761602</v>
+        <v>19.19038002851729</v>
       </c>
       <c r="Y54">
-        <v>129.8050321639627</v>
+        <v>131.8799153342727</v>
       </c>
       <c r="Z54">
         <v>163.5464935302734</v>
@@ -7007,16 +7007,16 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC54">
         <v>0.425</v>
       </c>
       <c r="AD54">
-        <v>0.7936888731884366</v>
+        <v>0.8063756824591346</v>
       </c>
       <c r="AE54">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF54">
         <v>137.735829909156</v>
@@ -7093,7 +7093,7 @@
         <v>23.45214913182408</v>
       </c>
       <c r="R55">
-        <v>160.7408311810777</v>
+        <v>158.3954315319789</v>
       </c>
       <c r="S55">
         <v>163.2196655273438</v>
@@ -7108,13 +7108,13 @@
         <v>0.425</v>
       </c>
       <c r="W55">
-        <v>0.9848128940942426</v>
+        <v>0.9704433042441407</v>
       </c>
       <c r="X55">
-        <v>21.53577967761602</v>
+        <v>19.19038002851729</v>
       </c>
       <c r="Y55">
-        <v>140.6095393050759</v>
+        <v>142.684422475386</v>
       </c>
       <c r="Z55">
         <v>163.2150726318359</v>
@@ -7123,16 +7123,16 @@
         <v>0</v>
       </c>
       <c r="AB55">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC55">
         <v>0.425</v>
       </c>
       <c r="AD55">
-        <v>0.8614984942122884</v>
+        <v>0.874211065035881</v>
       </c>
       <c r="AE55">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF55">
         <v>121.0600329464373</v>
@@ -7209,13 +7209,13 @@
         <v>23.32949409925816</v>
       </c>
       <c r="R56">
-        <v>170.2582650359318</v>
+        <v>167.9128653868331</v>
       </c>
       <c r="S56">
         <v>154.3109283447266</v>
       </c>
       <c r="T56">
-        <v>15.94733669120524</v>
+        <v>13.6019370421065</v>
       </c>
       <c r="U56">
         <v>0.85</v>
@@ -7227,10 +7227,10 @@
         <v>1</v>
       </c>
       <c r="X56">
-        <v>21.53577967761602</v>
+        <v>19.19038002851729</v>
       </c>
       <c r="Y56">
-        <v>148.4861840072244</v>
+        <v>150.5610671775344</v>
       </c>
       <c r="Z56">
         <v>154.3094787597656</v>
@@ -7239,16 +7239,16 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC56">
         <v>0.425</v>
       </c>
       <c r="AD56">
-        <v>0.9622622356102495</v>
+        <v>0.9757084813430879</v>
       </c>
       <c r="AE56">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF56">
         <v>122.6345730302216</v>
@@ -7325,7 +7325,7 @@
         <v>23.06649729239375</v>
       </c>
       <c r="R57">
-        <v>150.6615965146124</v>
+        <v>149.4505614244919</v>
       </c>
       <c r="S57">
         <v>153.7727508544922</v>
@@ -7340,13 +7340,13 @@
         <v>0.425</v>
       </c>
       <c r="W57">
-        <v>0.9797678436355493</v>
+        <v>0.9718923580024252</v>
       </c>
       <c r="X57">
-        <v>22.56333911293433</v>
+        <v>21.35230402281383</v>
       </c>
       <c r="Y57">
-        <v>127.0807718124002</v>
+        <v>129.1556549827102</v>
       </c>
       <c r="Z57">
         <v>153.768798828125</v>
@@ -7355,16 +7355,16 @@
         <v>0</v>
       </c>
       <c r="AB57">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC57">
         <v>0.425</v>
       </c>
       <c r="AD57">
-        <v>0.8264405573880085</v>
+        <v>0.8399340826423042</v>
       </c>
       <c r="AE57">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF57">
         <v>116.6905869720614</v>
@@ -7441,7 +7441,7 @@
         <v>22.87606047917264</v>
       </c>
       <c r="R58">
-        <v>139.7443469918362</v>
+        <v>138.5333119017157</v>
       </c>
       <c r="S58">
         <v>148.7952270507812</v>
@@ -7456,13 +7456,13 @@
         <v>0.425</v>
       </c>
       <c r="W58">
-        <v>0.9391722420245635</v>
+        <v>0.9310333042768681</v>
       </c>
       <c r="X58">
-        <v>22.56333911293433</v>
+        <v>21.35230402281383</v>
       </c>
       <c r="Y58">
-        <v>114.6453608382791</v>
+        <v>116.7202440085891</v>
       </c>
       <c r="Z58">
         <v>148.7915649414062</v>
@@ -7471,16 +7471,16 @@
         <v>0</v>
       </c>
       <c r="AB58">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC58">
         <v>0.425</v>
       </c>
       <c r="AD58">
-        <v>0.7705098127264549</v>
+        <v>0.7844547105513221</v>
       </c>
       <c r="AE58">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF58">
         <v>127.8469718828548</v>
@@ -7557,13 +7557,13 @@
         <v>22.64382640021926</v>
       </c>
       <c r="R59">
-        <v>150.6555525168155</v>
+        <v>150.4909066964649</v>
       </c>
       <c r="S59">
         <v>143.0128784179688</v>
       </c>
       <c r="T59">
-        <v>7.642674098846754</v>
+        <v>7.478028278496112</v>
       </c>
       <c r="U59">
         <v>0.85</v>
@@ -7575,10 +7575,10 @@
         <v>1</v>
       </c>
       <c r="X59">
-        <v>23.24648903860171</v>
+        <v>23.08184321825107</v>
       </c>
       <c r="Y59">
-        <v>135.2179792098611</v>
+        <v>137.2928623801711</v>
       </c>
       <c r="Z59">
         <v>143.0128479003906</v>
@@ -7587,16 +7587,16 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC59">
         <v>0.425</v>
       </c>
       <c r="AD59">
-        <v>0.945495325734939</v>
+        <v>0.9600036947435415</v>
       </c>
       <c r="AE59">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF59">
         <v>121.2202848773708</v>
@@ -7673,13 +7673,13 @@
         <v>22.3753065356421</v>
       </c>
       <c r="R60">
-        <v>138.1994788436665</v>
+        <v>138.0348330233159</v>
       </c>
       <c r="S60">
         <v>135.1491241455078</v>
       </c>
       <c r="T60">
-        <v>3.050354698158685</v>
+        <v>2.885708877808042</v>
       </c>
       <c r="U60">
         <v>0.85</v>
@@ -7691,10 +7691,10 @@
         <v>1</v>
       </c>
       <c r="X60">
-        <v>23.24648903860171</v>
+        <v>23.08184321825107</v>
       </c>
       <c r="Y60">
-        <v>122.1894839339822</v>
+        <v>124.2643671042922</v>
       </c>
       <c r="Z60">
         <v>135.1521148681641</v>
@@ -7703,16 +7703,16 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC60">
         <v>0.425</v>
       </c>
       <c r="AD60">
-        <v>0.9040885823590225</v>
+        <v>0.9194407888142005</v>
       </c>
       <c r="AE60">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF60">
         <v>122.8124937456794</v>
@@ -7789,13 +7789,13 @@
         <v>22.0513215355037</v>
       </c>
       <c r="R61">
-        <v>148.6486242228127</v>
+        <v>149.481799295092</v>
       </c>
       <c r="S61">
         <v>127.7220687866211</v>
       </c>
       <c r="T61">
-        <v>20.92655543619162</v>
+        <v>21.75973050847088</v>
       </c>
       <c r="U61">
         <v>0.85</v>
@@ -7807,19 +7807,19 @@
         <v>1</v>
       </c>
       <c r="X61">
-        <v>23.63229950232162</v>
+        <v>24.46547457460085</v>
       </c>
       <c r="Y61">
-        <v>131.5040729598611</v>
+        <v>133.5789561301711</v>
       </c>
       <c r="Z61">
         <v>127.7239074707031</v>
       </c>
       <c r="AA61">
-        <v>3.78016548915798</v>
+        <v>5.855048659467997</v>
       </c>
       <c r="AB61">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC61">
         <v>0.425</v>
@@ -7828,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="AE61">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF61">
         <v>137.3813543030604</v>
@@ -7905,13 +7905,13 @@
         <v>21.70554761101859</v>
       </c>
       <c r="R62">
-        <v>142.6878335278875</v>
+        <v>143.5210086001667</v>
       </c>
       <c r="S62">
         <v>118.0039291381836</v>
       </c>
       <c r="T62">
-        <v>24.68390438970391</v>
+        <v>25.51707946198314</v>
       </c>
       <c r="U62">
         <v>0.85</v>
@@ -7923,19 +7923,19 @@
         <v>1</v>
       </c>
       <c r="X62">
-        <v>23.63229950232162</v>
+        <v>24.46547457460085</v>
       </c>
       <c r="Y62">
-        <v>125.7466895003885</v>
+        <v>127.8215726706985</v>
       </c>
       <c r="Z62">
         <v>118.0060043334961</v>
       </c>
       <c r="AA62">
-        <v>7.740685166892362</v>
+        <v>9.815568337202365</v>
       </c>
       <c r="AB62">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC62">
         <v>0.425</v>
@@ -7944,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="AE62">
-        <v>22.98785307920912</v>
+        <v>25.06273624951913</v>
       </c>
       <c r="AF62">
         <v>120.3814481189629</v>
@@ -8021,13 +8021,13 @@
         <v>21.30806439972562</v>
       </c>
       <c r="R63">
-        <v>145.0962436658257</v>
+        <v>146.910528320488</v>
       </c>
       <c r="S63">
         <v>107.8020401000977</v>
       </c>
       <c r="T63">
-        <v>37.29420356572803</v>
+        <v>39.10848822039031</v>
       </c>
       <c r="U63">
         <v>0.85</v>
@@ -8039,19 +8039,19 @@
         <v>1</v>
       </c>
       <c r="X63">
-        <v>23.75809500501842</v>
+        <v>25.57237965968068</v>
       </c>
       <c r="Y63">
-        <v>127.9583342916902</v>
+        <v>130.9528168332625</v>
       </c>
       <c r="Z63">
         <v>107.7956008911133</v>
       </c>
       <c r="AA63">
-        <v>20.16273340057697</v>
+        <v>23.15721594214921</v>
       </c>
       <c r="AB63">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC63">
         <v>0.425</v>
@@ -8060,7 +8060,7 @@
         <v>1</v>
       </c>
       <c r="AE63">
-        <v>22.88086725527654</v>
+        <v>25.87534979684879</v>
       </c>
       <c r="AF63">
         <v>133.3425587799278</v>
@@ -8137,13 +8137,13 @@
         <v>20.87515939026344</v>
       </c>
       <c r="R64">
-        <v>122.2530064332981</v>
+        <v>124.0672910879603</v>
       </c>
       <c r="S64">
         <v>96.02672576904297</v>
       </c>
       <c r="T64">
-        <v>26.22628066425511</v>
+        <v>28.04056531891737</v>
       </c>
       <c r="U64">
         <v>0.85</v>
@@ -8155,19 +8155,19 @@
         <v>1</v>
       </c>
       <c r="X64">
-        <v>23.75809500501842</v>
+        <v>25.57237965968068</v>
       </c>
       <c r="Y64">
-        <v>122.4428493673738</v>
+        <v>125.4373319089461</v>
       </c>
       <c r="Z64">
         <v>96.02329254150391</v>
       </c>
       <c r="AA64">
-        <v>26.41955682586993</v>
+        <v>29.41403936744219</v>
       </c>
       <c r="AB64">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC64">
         <v>0.425</v>
@@ -8176,7 +8176,7 @@
         <v>1</v>
       </c>
       <c r="AE64">
-        <v>22.88086725527654</v>
+        <v>25.87534979684879</v>
       </c>
       <c r="AF64">
         <v>124.0700576373458</v>
@@ -8253,13 +8253,13 @@
         <v>20.39623813110228</v>
       </c>
       <c r="R65">
-        <v>125.1040806422806</v>
+        <v>127.9090978803695</v>
       </c>
       <c r="S65">
         <v>84.79279327392578</v>
       </c>
       <c r="T65">
-        <v>40.31128736835487</v>
+        <v>43.11630460644372</v>
       </c>
       <c r="U65">
         <v>0.85</v>
@@ -8271,19 +8271,19 @@
         <v>1</v>
       </c>
       <c r="X65">
-        <v>23.65288648965571</v>
+        <v>26.45790372774455</v>
       </c>
       <c r="Y65">
-        <v>125.606622487491</v>
+        <v>128.6011050290633</v>
       </c>
       <c r="Z65">
         <v>84.79557800292969</v>
       </c>
       <c r="AA65">
-        <v>40.81104448456134</v>
+        <v>43.8055270261336</v>
       </c>
       <c r="AB65">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC65">
         <v>0.425</v>
@@ -8292,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="AE65">
-        <v>22.88086725527654</v>
+        <v>25.87534979684879</v>
       </c>
       <c r="AF65">
         <v>122.8772098979845</v>
@@ -8369,13 +8369,13 @@
         <v>19.9440871434785</v>
       </c>
       <c r="R66">
-        <v>131.0770796657906</v>
+        <v>133.8820969038795</v>
       </c>
       <c r="S66">
         <v>72.67034149169922</v>
       </c>
       <c r="T66">
-        <v>58.4067381740914</v>
+        <v>61.21175541218025</v>
       </c>
       <c r="U66">
         <v>0.85</v>
@@ -8387,19 +8387,19 @@
         <v>1</v>
       </c>
       <c r="X66">
-        <v>23.65288648965571</v>
+        <v>26.45790372774455</v>
       </c>
       <c r="Y66">
-        <v>113.4892743373801</v>
+        <v>117.2361563645306</v>
       </c>
       <c r="Z66">
         <v>72.67194366455078</v>
       </c>
       <c r="AA66">
-        <v>40.81733067282934</v>
+        <v>44.56421269997981</v>
       </c>
       <c r="AB66">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC66">
         <v>0.425</v>
@@ -8408,7 +8408,7 @@
         <v>1</v>
       </c>
       <c r="AE66">
-        <v>22.20651472284141</v>
+        <v>25.95339674999187</v>
       </c>
       <c r="AF66">
         <v>124.4741795383873</v>
@@ -8485,13 +8485,13 @@
         <v>19.65569142553594</v>
       </c>
       <c r="R67">
-        <v>149.3244970599554</v>
+        <v>154.0094893425818</v>
       </c>
       <c r="S67">
         <v>59.55197906494141</v>
       </c>
       <c r="T67">
-        <v>89.77251799501403</v>
+        <v>94.45751027764038</v>
       </c>
       <c r="U67">
         <v>0.85</v>
@@ -8503,19 +8503,19 @@
         <v>1</v>
       </c>
       <c r="X67">
-        <v>22.4813306995693</v>
+        <v>27.16632298219564</v>
       </c>
       <c r="Y67">
-        <v>132.1033427069593</v>
+        <v>136.4321587112366</v>
       </c>
       <c r="Z67">
         <v>59.55376052856445</v>
       </c>
       <c r="AA67">
-        <v>72.54958217839484</v>
+        <v>76.87839818267219</v>
       </c>
       <c r="AB67">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC67">
         <v>0.425</v>
@@ -8524,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="AE67">
-        <v>20.65616098548699</v>
+        <v>24.98497698976434</v>
       </c>
       <c r="AF67">
         <v>120.9682972590903</v>
@@ -8601,13 +8601,13 @@
         <v>19.44678072315589</v>
       </c>
       <c r="R68">
-        <v>140.8778377779121</v>
+        <v>145.5628300605384</v>
       </c>
       <c r="S68">
         <v>46.49455261230469</v>
       </c>
       <c r="T68">
-        <v>94.38328516560739</v>
+        <v>99.06827744823374</v>
       </c>
       <c r="U68">
         <v>0.85</v>
@@ -8619,19 +8619,19 @@
         <v>1</v>
       </c>
       <c r="X68">
-        <v>22.4813306995693</v>
+        <v>27.16632298219564</v>
       </c>
       <c r="Y68">
-        <v>124.559792863605</v>
+        <v>128.8886088678823</v>
       </c>
       <c r="Z68">
         <v>46.49905395507812</v>
       </c>
       <c r="AA68">
-        <v>78.06073890852684</v>
+        <v>82.38955491280421</v>
       </c>
       <c r="AB68">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC68">
         <v>0.425</v>
@@ -8640,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="AE68">
-        <v>20.65616098548699</v>
+        <v>24.98497698976434</v>
       </c>
       <c r="AF68">
         <v>133.858214337441</v>
@@ -8717,16 +8717,16 @@
         <v>19.27451698476038</v>
       </c>
       <c r="R69">
-        <v>138.9350041328896</v>
+        <v>143.6199964155159</v>
       </c>
       <c r="S69">
         <v>34.93395233154297</v>
       </c>
       <c r="T69">
-        <v>104.0010518013466</v>
+        <v>108.6860440839729</v>
       </c>
       <c r="U69">
-        <v>0.8327854547242225</v>
+        <v>0.8312707142011676</v>
       </c>
       <c r="V69">
         <v>0.425</v>
@@ -8735,19 +8735,19 @@
         <v>1</v>
       </c>
       <c r="X69">
-        <v>22.4813306995693</v>
+        <v>27.16632298219564</v>
       </c>
       <c r="Y69">
-        <v>122.8849809343984</v>
+        <v>127.2137969386758</v>
       </c>
       <c r="Z69">
         <v>34.93400192260742</v>
       </c>
       <c r="AA69">
-        <v>87.95097901179102</v>
+        <v>92.27979501606836</v>
       </c>
       <c r="AB69">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC69">
         <v>0.425</v>
@@ -8756,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="AE69">
-        <v>20.65616098548699</v>
+        <v>24.98497698976434</v>
       </c>
       <c r="AF69">
         <v>128.7390403556244</v>
@@ -8833,16 +8833,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R70">
-        <v>148.0909778764179</v>
+        <v>152.7759701590442</v>
       </c>
       <c r="S70">
         <v>24.62921524047852</v>
       </c>
       <c r="T70">
-        <v>123.4617626359394</v>
+        <v>128.1467549185657</v>
       </c>
       <c r="U70">
-        <v>0.8327854547242225</v>
+        <v>0.8312707142011676</v>
       </c>
       <c r="V70">
         <v>0.425</v>
@@ -8851,19 +8851,19 @@
         <v>1</v>
       </c>
       <c r="X70">
-        <v>22.4813306995693</v>
+        <v>27.16632298219564</v>
       </c>
       <c r="Y70">
-        <v>131.5794516647979</v>
+        <v>135.9082676690753</v>
       </c>
       <c r="Z70">
         <v>24.62500953674316</v>
       </c>
       <c r="AA70">
-        <v>106.9544421280548</v>
+        <v>111.2832581323322</v>
       </c>
       <c r="AB70">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC70">
         <v>0.425</v>
@@ -8872,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="AE70">
-        <v>20.65616098548699</v>
+        <v>24.98497698976434</v>
       </c>
       <c r="AF70">
         <v>128.5031864268297</v>
@@ -8949,16 +8949,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R71">
-        <v>144.663509615335</v>
+        <v>147.5543488465796</v>
       </c>
       <c r="S71">
         <v>16.37712860107422</v>
       </c>
       <c r="T71">
-        <v>128.2863810142607</v>
+        <v>131.1772202455054</v>
       </c>
       <c r="U71">
-        <v>0.8327854547242225</v>
+        <v>0.8131229861935092</v>
       </c>
       <c r="V71">
         <v>0.425</v>
@@ -8967,19 +8967,19 @@
         <v>1</v>
       </c>
       <c r="X71">
-        <v>18.27548375095099</v>
+        <v>21.16632298219564</v>
       </c>
       <c r="Y71">
-        <v>112.2295281947479</v>
+        <v>132.4660779165226</v>
       </c>
       <c r="Z71">
         <v>16.37812232971191</v>
       </c>
       <c r="AA71">
-        <v>95.85140586503596</v>
+        <v>116.0879555868107</v>
       </c>
       <c r="AB71">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC71">
         <v>0.425</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>20.23654972177473</v>
       </c>
       <c r="AF71">
         <v>132.6416478667044</v>
@@ -9065,16 +9065,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R72">
-        <v>170.7126647884328</v>
+        <v>171.0927992659385</v>
       </c>
       <c r="S72">
         <v>7.840934753417969</v>
       </c>
       <c r="T72">
-        <v>162.8717300350148</v>
+        <v>163.2518645125206</v>
       </c>
       <c r="U72">
-        <v>0.8327854547242225</v>
+        <v>0.795663772971049</v>
       </c>
       <c r="V72">
         <v>0.425</v>
@@ -9083,19 +9083,19 @@
         <v>0.5681869387626648</v>
       </c>
       <c r="X72">
-        <v>14.78618850468988</v>
+        <v>15.16632298219564</v>
       </c>
       <c r="Y72">
-        <v>130.6219076393167</v>
+        <v>150.8584573610914</v>
       </c>
       <c r="Z72">
         <v>7.843290328979492</v>
       </c>
       <c r="AA72">
-        <v>122.7786173103372</v>
+        <v>143.0151670321119</v>
       </c>
       <c r="AB72">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC72">
         <v>0.425</v>
@@ -9104,7 +9104,7 @@
         <v>0.5686580538749695</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>20.23654972177473</v>
       </c>
       <c r="AF72">
         <v>151.889070653649</v>
@@ -9181,16 +9181,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R73">
-        <v>192.9246517321587</v>
+        <v>193.3047862096644</v>
       </c>
       <c r="S73">
         <v>3.505656957626343</v>
       </c>
       <c r="T73">
-        <v>189.4189947745323</v>
+        <v>189.7991292520381</v>
       </c>
       <c r="U73">
-        <v>0.8146717478379195</v>
+        <v>0.7774271619127533</v>
       </c>
       <c r="V73">
         <v>0.425</v>
@@ -9199,19 +9199,19 @@
         <v>0</v>
       </c>
       <c r="X73">
-        <v>14.78618850468988</v>
+        <v>15.16632298219564</v>
       </c>
       <c r="Y73">
-        <v>152.8102587042246</v>
+        <v>173.0468084259993</v>
       </c>
       <c r="Z73">
         <v>3.502935409545898</v>
       </c>
       <c r="AA73">
-        <v>149.3073232946787</v>
+        <v>169.5438730164534</v>
       </c>
       <c r="AB73">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC73">
         <v>0.425</v>
@@ -9220,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>20.23654972177473</v>
       </c>
       <c r="AF73">
         <v>141.7552014020956</v>
@@ -9297,16 +9297,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R74">
-        <v>185.4175468654519</v>
+        <v>185.7976813429576</v>
       </c>
       <c r="S74">
         <v>1.646571755409241</v>
       </c>
       <c r="T74">
-        <v>183.7709751100426</v>
+        <v>184.1511095875484</v>
       </c>
       <c r="U74">
-        <v>0.793556403062161</v>
+        <v>0.7561889129650021</v>
       </c>
       <c r="V74">
         <v>0.425</v>
@@ -9315,19 +9315,19 @@
         <v>0</v>
       </c>
       <c r="X74">
-        <v>14.78618850468988</v>
+        <v>15.16632298219564</v>
       </c>
       <c r="Y74">
-        <v>145.5217535198123</v>
+        <v>165.758303241587</v>
       </c>
       <c r="Z74">
         <v>1.6515873670578</v>
       </c>
       <c r="AA74">
-        <v>143.8701661527545</v>
+        <v>164.1067158745292</v>
       </c>
       <c r="AB74">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC74">
         <v>0.425</v>
@@ -9336,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>20.23654972177473</v>
       </c>
       <c r="AF74">
         <v>120.372621999357</v>
@@ -9413,16 +9413,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R75">
-        <v>206.4982173431081</v>
+        <v>206.8783518206138</v>
       </c>
       <c r="S75">
         <v>0.804743230342865</v>
       </c>
       <c r="T75">
-        <v>205.6934741127652</v>
+        <v>206.073608590271</v>
       </c>
       <c r="U75">
-        <v>0.7688157732949276</v>
+        <v>0.731325379025776</v>
       </c>
       <c r="V75">
         <v>0.55</v>
@@ -9431,19 +9431,19 @@
         <v>0</v>
       </c>
       <c r="X75">
-        <v>14.78618850468988</v>
+        <v>15.16632298219564</v>
       </c>
       <c r="Y75">
-        <v>158.2622703126906</v>
+        <v>178.4988200344653</v>
       </c>
       <c r="Z75">
         <v>0.8011622428894043</v>
       </c>
       <c r="AA75">
-        <v>157.4611080698012</v>
+        <v>177.6976577915759</v>
       </c>
       <c r="AB75">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC75">
         <v>0.55</v>
@@ -9452,7 +9452,7 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>20.23654972177473</v>
       </c>
       <c r="AF75">
         <v>141.8631311559428</v>
@@ -9529,16 +9529,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R76">
-        <v>203.4192536419815</v>
+        <v>203.7993881194872</v>
       </c>
       <c r="S76">
         <v>1.200266718864441</v>
       </c>
       <c r="T76">
-        <v>202.2189869231171</v>
+        <v>202.5991214006228</v>
       </c>
       <c r="U76">
-        <v>0.7403038688805331</v>
+        <v>0.7026905704393889</v>
       </c>
       <c r="V76">
         <v>0.55</v>
@@ -9547,19 +9547,19 @@
         <v>0</v>
       </c>
       <c r="X76">
-        <v>14.78618850468988</v>
+        <v>15.16632298219564</v>
       </c>
       <c r="Y76">
-        <v>160.5362444476</v>
+        <v>180.7727941693747</v>
       </c>
       <c r="Z76">
         <v>1.198043584823608</v>
       </c>
       <c r="AA76">
-        <v>159.3382008627764</v>
+        <v>179.5747505845511</v>
       </c>
       <c r="AB76">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC76">
         <v>0.55</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>20.23654972177473</v>
       </c>
       <c r="AF76">
         <v>134.4725317350086</v>
@@ -9645,16 +9645,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R77">
-        <v>183.4279400716821</v>
+        <v>183.8080745491879</v>
       </c>
       <c r="S77">
         <v>0.7062832713127136</v>
       </c>
       <c r="T77">
-        <v>182.7216568003694</v>
+        <v>183.1017912778752</v>
       </c>
       <c r="U77">
-        <v>0.6933020493251907</v>
+        <v>0.6555131734954854</v>
       </c>
       <c r="V77">
         <v>0.55</v>
@@ -9663,19 +9663,19 @@
         <v>0</v>
       </c>
       <c r="X77">
-        <v>14.78618850468988</v>
+        <v>15.16632298219564</v>
       </c>
       <c r="Y77">
-        <v>146.0459300331389</v>
+        <v>161.7498900900145</v>
       </c>
       <c r="Z77">
         <v>0.7013470530509949</v>
       </c>
       <c r="AA77">
-        <v>145.3445829800879</v>
+        <v>161.0485430369635</v>
       </c>
       <c r="AB77">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC77">
         <v>0.55</v>
@@ -9684,7 +9684,7 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>15.70396005687555</v>
       </c>
       <c r="AF77">
         <v>153.2128648000763</v>
@@ -9761,16 +9761,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R78">
-        <v>203.345389689657</v>
+        <v>212.9825910750626</v>
       </c>
       <c r="S78">
         <v>0.6419051289558411</v>
       </c>
       <c r="T78">
-        <v>202.7034845607012</v>
+        <v>212.3406859461067</v>
       </c>
       <c r="U78">
-        <v>0.6592070669731669</v>
+        <v>0.621295286971469</v>
       </c>
       <c r="V78">
         <v>0.55</v>
@@ -9779,19 +9779,19 @@
         <v>0</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>9.637201385405561</v>
       </c>
       <c r="Y78">
-        <v>180.5913442123832</v>
+        <v>196.2953042692588</v>
       </c>
       <c r="Z78">
         <v>0.647027313709259</v>
       </c>
       <c r="AA78">
-        <v>179.9443168986739</v>
+        <v>195.6482769555495</v>
       </c>
       <c r="AB78">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC78">
         <v>0.55</v>
@@ -9800,7 +9800,7 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>15.70396005687555</v>
       </c>
       <c r="AF78">
         <v>156.0160346367153</v>
@@ -9877,16 +9877,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R79">
-        <v>165.5397570328657</v>
+        <v>170.6553590149084</v>
       </c>
       <c r="S79">
         <v>0.5416377782821655</v>
       </c>
       <c r="T79">
-        <v>164.9981192545835</v>
+        <v>170.1137212366262</v>
       </c>
       <c r="U79">
-        <v>0.6246459782748583</v>
+        <v>0.5836183213225307</v>
       </c>
       <c r="V79">
         <v>0.55</v>
@@ -9895,19 +9895,19 @@
         <v>0</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y79">
-        <v>143.1533565580705</v>
+        <v>158.8573166149461</v>
       </c>
       <c r="Z79">
         <v>0.5384072065353394</v>
       </c>
       <c r="AA79">
-        <v>142.6149493515352</v>
+        <v>158.3189094084107</v>
       </c>
       <c r="AB79">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC79">
         <v>0.55</v>
@@ -9916,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>15.70396005687555</v>
       </c>
       <c r="AF79">
         <v>168.966572365507</v>
@@ -9993,16 +9993,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R80">
-        <v>180.4849546678745</v>
+        <v>185.6005566499173</v>
       </c>
       <c r="S80">
         <v>0.2434973418712616</v>
       </c>
       <c r="T80">
-        <v>180.2414573260033</v>
+        <v>185.357059308046</v>
       </c>
       <c r="U80">
-        <v>0.5893211731798135</v>
+        <v>0.5466395520041604</v>
       </c>
       <c r="V80">
         <v>0.55</v>
@@ -10011,19 +10011,19 @@
         <v>0</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y80">
-        <v>162.2461470389363</v>
+        <v>177.9501070958118</v>
       </c>
       <c r="Z80">
         <v>0.2364100217819214</v>
       </c>
       <c r="AA80">
-        <v>162.0097370171544</v>
+        <v>177.7136970740299</v>
       </c>
       <c r="AB80">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC80">
         <v>0.55</v>
@@ -10032,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>15.70396005687555</v>
       </c>
       <c r="AF80">
         <v>165.6872856778263</v>
@@ -10109,16 +10109,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R81">
-        <v>186.9904688232914</v>
+        <v>192.1060708053341</v>
       </c>
       <c r="S81">
         <v>0.1437614858150482</v>
       </c>
       <c r="T81">
-        <v>186.8467073374763</v>
+        <v>191.9623093195191</v>
       </c>
       <c r="U81">
-        <v>0.5550716773756873</v>
+        <v>0.5107360919767088</v>
       </c>
       <c r="V81">
         <v>0.55</v>
@@ -10127,19 +10127,19 @@
         <v>0</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y81">
-        <v>168.4808851571805</v>
+        <v>184.1848452140561</v>
       </c>
       <c r="Z81">
         <v>0.1412963569164276</v>
       </c>
       <c r="AA81">
-        <v>168.3395888002641</v>
+        <v>184.0435488571396</v>
       </c>
       <c r="AB81">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC81">
         <v>0.55</v>
@@ -10148,7 +10148,7 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>15.70396005687555</v>
       </c>
       <c r="AF81">
         <v>189.4598137954029</v>
@@ -10225,16 +10225,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R82">
-        <v>190.8054670279097</v>
+        <v>195.9210690099524</v>
       </c>
       <c r="S82">
         <v>0.05145746842026711</v>
       </c>
       <c r="T82">
-        <v>190.7540095594894</v>
+        <v>195.8696115415321</v>
       </c>
       <c r="U82">
-        <v>0.5194824052781575</v>
+        <v>0.4734928556558535</v>
       </c>
       <c r="V82">
         <v>0.55</v>
@@ -10243,19 +10243,19 @@
         <v>0</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y82">
-        <v>172.8619427616757</v>
+        <v>188.5659028185513</v>
       </c>
       <c r="Z82">
         <v>0.05605533346533775</v>
       </c>
       <c r="AA82">
-        <v>172.8058874282104</v>
+        <v>188.509847485086</v>
       </c>
       <c r="AB82">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC82">
         <v>0.55</v>
@@ -10264,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>15.70396005687555</v>
       </c>
       <c r="AF82">
         <v>178.4693269715775</v>
@@ -10341,16 +10341,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R83">
-        <v>177.7794631206108</v>
+        <v>182.8950651026535</v>
       </c>
       <c r="S83">
         <v>0.0385642945766449</v>
       </c>
       <c r="T83">
-        <v>177.7408988260341</v>
+        <v>182.8565008080768</v>
       </c>
       <c r="U83">
-        <v>0.4783516571620057</v>
+        <v>0.4307081433163763</v>
       </c>
       <c r="V83">
         <v>0.55</v>
@@ -10359,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y83">
         <v>160.7305954467269</v>
@@ -10371,7 +10371,7 @@
         <v>160.6925482447954</v>
       </c>
       <c r="AB83">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC83">
         <v>0.55</v>
@@ -10457,16 +10457,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R84">
-        <v>190.2886266708373</v>
+        <v>195.4042286528801</v>
       </c>
       <c r="S84">
         <v>0.03798231482505798</v>
       </c>
       <c r="T84">
-        <v>190.2506443560123</v>
+        <v>195.366246338055</v>
       </c>
       <c r="U84">
-        <v>0.4403186536240242</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V84">
         <v>0.55</v>
@@ -10475,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y84">
         <v>177.361122043253</v>
@@ -10487,7 +10487,7 @@
         <v>177.3225285796533</v>
       </c>
       <c r="AB84">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC84">
         <v>0.55</v>
@@ -10499,13 +10499,13 @@
         <v>0</v>
       </c>
       <c r="AF84">
-        <v>196.1609730792178</v>
+        <v>196.5372498585369</v>
       </c>
       <c r="AG84">
         <v>0.03717801719903946</v>
       </c>
       <c r="AH84">
-        <v>196.1237950620187</v>
+        <v>196.5000718413379</v>
       </c>
       <c r="AI84">
         <v>0.3641225964227157</v>
@@ -10573,16 +10573,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R85">
-        <v>170.1314246333323</v>
+        <v>175.247026615375</v>
       </c>
       <c r="S85">
         <v>0.03926149383187294</v>
       </c>
       <c r="T85">
-        <v>170.0921631395004</v>
+        <v>175.2077651215431</v>
       </c>
       <c r="U85">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V85">
         <v>0.55</v>
@@ -10591,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y85">
         <v>158.4513773238283</v>
@@ -10603,7 +10603,7 @@
         <v>158.4141949703913</v>
       </c>
       <c r="AB85">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC85">
         <v>0.55</v>
@@ -10615,13 +10615,13 @@
         <v>0</v>
       </c>
       <c r="AF85">
-        <v>192.2195115495172</v>
+        <v>192.5261720531633</v>
       </c>
       <c r="AG85">
         <v>0.03743105381727219</v>
       </c>
       <c r="AH85">
-        <v>192.1820804956999</v>
+        <v>192.488740999346</v>
       </c>
       <c r="AI85">
         <v>0.3641225964227157</v>
@@ -10689,16 +10689,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R86">
-        <v>181.1841856657589</v>
+        <v>186.2997876478017</v>
       </c>
       <c r="S86">
         <v>0.03887698799371719</v>
       </c>
       <c r="T86">
-        <v>181.1453086777652</v>
+        <v>186.2609106598079</v>
       </c>
       <c r="U86">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V86">
         <v>0.55</v>
@@ -10707,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>5.115601982042711</v>
       </c>
       <c r="Y86">
         <v>173.1193871727827</v>
@@ -10719,7 +10719,7 @@
         <v>173.0822372591737</v>
       </c>
       <c r="AB86">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC86">
         <v>0.55</v>
@@ -10731,13 +10731,13 @@
         <v>0</v>
       </c>
       <c r="AF86">
-        <v>202.5739841949827</v>
+        <v>203.5295986540478</v>
       </c>
       <c r="AG86">
         <v>0.03906415030360222</v>
       </c>
       <c r="AH86">
-        <v>202.5349200446791</v>
+        <v>203.4905345037442</v>
       </c>
       <c r="AI86">
         <v>0.3641225964227157</v>
@@ -10805,16 +10805,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R87">
-        <v>188.123722323456</v>
+        <v>189.3209767152577</v>
       </c>
       <c r="S87">
         <v>0.0382227748632431</v>
       </c>
       <c r="T87">
-        <v>188.0854995485927</v>
+        <v>189.2827539403945</v>
       </c>
       <c r="U87">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V87">
         <v>0.55</v>
@@ -10823,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y87">
         <v>180.6609824046217</v>
@@ -10835,7 +10835,7 @@
         <v>180.6241753518306</v>
       </c>
       <c r="AB87">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC87">
         <v>0.55</v>
@@ -10847,13 +10847,13 @@
         <v>0</v>
       </c>
       <c r="AF87">
-        <v>191.8698215039661</v>
+        <v>192.9871487347686</v>
       </c>
       <c r="AG87">
         <v>0.03885768726468086</v>
       </c>
       <c r="AH87">
-        <v>191.8309638167014</v>
+        <v>192.9482910475039</v>
       </c>
       <c r="AI87">
         <v>0.3641225964227157</v>
@@ -10921,16 +10921,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R88">
-        <v>181.846347640269</v>
+        <v>183.0436020320708</v>
       </c>
       <c r="S88">
         <v>0.03895450383424759</v>
       </c>
       <c r="T88">
-        <v>181.8073931364348</v>
+        <v>183.0046475282365</v>
       </c>
       <c r="U88">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V88">
         <v>0.55</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y88">
         <v>177.1579124074234</v>
@@ -10951,7 +10951,7 @@
         <v>177.1192190054609</v>
       </c>
       <c r="AB88">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC88">
         <v>0.55</v>
@@ -10963,13 +10963,13 @@
         <v>0</v>
       </c>
       <c r="AF88">
-        <v>150.5816142188011</v>
+        <v>151.7597145971738</v>
       </c>
       <c r="AG88">
         <v>0.03671123087406158</v>
       </c>
       <c r="AH88">
-        <v>150.5449029879271</v>
+        <v>151.7230033662997</v>
       </c>
       <c r="AI88">
         <v>0.3641225964227157</v>
@@ -11037,16 +11037,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R89">
-        <v>165.4179369616209</v>
+        <v>166.6151913534227</v>
       </c>
       <c r="S89">
         <v>0.03802125155925751</v>
       </c>
       <c r="T89">
-        <v>165.3799157100617</v>
+        <v>166.5771701018634</v>
       </c>
       <c r="U89">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V89">
         <v>0.55</v>
@@ -11055,7 +11055,7 @@
         <v>0</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y89">
         <v>162.9565033621689</v>
@@ -11067,7 +11067,7 @@
         <v>162.9175644933781</v>
       </c>
       <c r="AB89">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC89">
         <v>0.55</v>
@@ -11079,13 +11079,13 @@
         <v>0</v>
       </c>
       <c r="AF89">
-        <v>168.6035388906496</v>
+        <v>170.5598301959756</v>
       </c>
       <c r="AG89">
         <v>0.03851545229554176</v>
       </c>
       <c r="AH89">
-        <v>168.5650234383541</v>
+        <v>170.5213147436801</v>
       </c>
       <c r="AI89">
         <v>0.3641225964227157</v>
@@ -11153,16 +11153,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R90">
-        <v>183.5560504913758</v>
+        <v>184.7533048831776</v>
       </c>
       <c r="S90">
         <v>0.03700482100248337</v>
       </c>
       <c r="T90">
-        <v>183.5190456703733</v>
+        <v>184.7163000621751</v>
       </c>
       <c r="U90">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V90">
         <v>0.55</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y90">
         <v>191.1765667498161</v>
@@ -11183,7 +11183,7 @@
         <v>191.1388129331221</v>
       </c>
       <c r="AB90">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC90">
         <v>0.55</v>
@@ -11195,13 +11195,13 @@
         <v>0</v>
       </c>
       <c r="AF90">
-        <v>128.4034699337133</v>
+        <v>130.6564126174539</v>
       </c>
       <c r="AG90">
         <v>0.03698307648301125</v>
       </c>
       <c r="AH90">
-        <v>128.3664868572303</v>
+        <v>130.6194295409709</v>
       </c>
       <c r="AI90">
         <v>0.3641225964227157</v>
@@ -11269,16 +11269,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R91">
-        <v>175.4564650330732</v>
+        <v>176.653719424875</v>
       </c>
       <c r="S91">
         <v>0.03679941222071648</v>
       </c>
       <c r="T91">
-        <v>175.4196656208525</v>
+        <v>176.6169200126543</v>
       </c>
       <c r="U91">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V91">
         <v>0.425</v>
@@ -11287,7 +11287,7 @@
         <v>0</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y91">
         <v>184.5006703916129</v>
@@ -11299,7 +11299,7 @@
         <v>184.4612688305911</v>
       </c>
       <c r="AB91">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC91">
         <v>0.425</v>
@@ -11311,13 +11311,13 @@
         <v>0</v>
       </c>
       <c r="AF91">
-        <v>119.6630970154785</v>
+        <v>122.114658854226</v>
       </c>
       <c r="AG91">
         <v>0.03855536878108978</v>
       </c>
       <c r="AH91">
-        <v>119.6245416466974</v>
+        <v>122.0761034854449</v>
       </c>
       <c r="AI91">
         <v>0.3641225964227157</v>
@@ -11385,16 +11385,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R92">
-        <v>143.6669806080582</v>
+        <v>144.86423499986</v>
       </c>
       <c r="S92">
         <v>0.03827942907810211</v>
       </c>
       <c r="T92">
-        <v>143.6287011789801</v>
+        <v>144.8259555707819</v>
       </c>
       <c r="U92">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V92">
         <v>0.425</v>
@@ -11403,7 +11403,7 @@
         <v>0</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y92">
         <v>146.0134675814921</v>
@@ -11415,7 +11415,7 @@
         <v>145.9762471146101</v>
       </c>
       <c r="AB92">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC92">
         <v>0.425</v>
@@ -11427,13 +11427,13 @@
         <v>0</v>
       </c>
       <c r="AF92">
-        <v>109.6936766381737</v>
+        <v>112.2820248857585</v>
       </c>
       <c r="AG92">
         <v>0.03877221047878265</v>
       </c>
       <c r="AH92">
-        <v>109.654904427695</v>
+        <v>112.2432526752797</v>
       </c>
       <c r="AI92">
         <v>0.3641225964227157</v>
@@ -11501,16 +11501,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R93">
-        <v>157.7681650680533</v>
+        <v>158.9654194598551</v>
       </c>
       <c r="S93">
         <v>0.03657148033380508</v>
       </c>
       <c r="T93">
-        <v>157.7315935877195</v>
+        <v>158.9288479795213</v>
       </c>
       <c r="U93">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V93">
         <v>0.425</v>
@@ -11519,7 +11519,7 @@
         <v>0</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y93">
         <v>161.9313679292885</v>
@@ -11531,7 +11531,7 @@
         <v>161.8959070064215</v>
       </c>
       <c r="AB93">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC93">
         <v>0.425</v>
@@ -11543,13 +11543,13 @@
         <v>0</v>
       </c>
       <c r="AF93">
-        <v>99.02562268828486</v>
+        <v>101.7157712260544</v>
       </c>
       <c r="AG93">
         <v>0.03611239790916443</v>
       </c>
       <c r="AH93">
-        <v>98.98951029037569</v>
+        <v>101.6796588281453</v>
       </c>
       <c r="AI93">
         <v>0.3641225964227157</v>
@@ -11617,16 +11617,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R94">
-        <v>128.3244842101504</v>
+        <v>129.5217386019521</v>
       </c>
       <c r="S94">
         <v>0.03760893642902374</v>
       </c>
       <c r="T94">
-        <v>128.2868752737213</v>
+        <v>129.4841296655231</v>
       </c>
       <c r="U94">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V94">
         <v>0.425</v>
@@ -11635,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.197254391801772</v>
       </c>
       <c r="Y94">
         <v>133.7920784430643</v>
@@ -11647,7 +11647,7 @@
         <v>133.7552309559723</v>
       </c>
       <c r="AB94">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC94">
         <v>0.425</v>
@@ -11659,13 +11659,13 @@
         <v>0</v>
       </c>
       <c r="AF94">
-        <v>87.44396671058502</v>
+        <v>90.22068074299874</v>
       </c>
       <c r="AG94">
         <v>0.03788449987769127</v>
       </c>
       <c r="AH94">
-        <v>87.40608221070732</v>
+        <v>90.18279624312105</v>
       </c>
       <c r="AI94">
         <v>0.3641225964227157</v>
@@ -11733,16 +11733,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R95">
-        <v>143.3226278592511</v>
+        <v>141.6756163664364</v>
       </c>
       <c r="S95">
         <v>0.03843317925930023</v>
       </c>
       <c r="T95">
-        <v>143.2841946799918</v>
+        <v>141.6371831871771</v>
       </c>
       <c r="U95">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V95">
         <v>0.3</v>
@@ -11751,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>-1.647011492814686</v>
       </c>
       <c r="Y95">
         <v>149.5244435842275</v>
@@ -11763,7 +11763,7 @@
         <v>149.4879921364724</v>
       </c>
       <c r="AB95">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC95">
         <v>0.3</v>
@@ -11775,13 +11775,13 @@
         <v>0</v>
       </c>
       <c r="AF95">
-        <v>70.10800808943893</v>
+        <v>72.97040608581192</v>
       </c>
       <c r="AG95">
         <v>0.03946569561958313</v>
       </c>
       <c r="AH95">
-        <v>70.06854239381934</v>
+        <v>72.93094039019233</v>
       </c>
       <c r="AI95">
         <v>0.3641225964227157</v>
@@ -11849,16 +11849,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R96">
-        <v>102.3158761929852</v>
+        <v>100.6688647001706</v>
       </c>
       <c r="S96">
         <v>0.03528690338134766</v>
       </c>
       <c r="T96">
-        <v>102.2805892896039</v>
+        <v>100.6335777967892</v>
       </c>
       <c r="U96">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V96">
         <v>0.3</v>
@@ -11867,7 +11867,7 @@
         <v>0</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>-1.647011492814686</v>
       </c>
       <c r="Y96">
         <v>110.0081601689913</v>
@@ -11879,7 +11879,7 @@
         <v>109.9721661794343</v>
       </c>
       <c r="AB96">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC96">
         <v>0.3</v>
@@ -11891,13 +11891,13 @@
         <v>0</v>
       </c>
       <c r="AF96">
-        <v>76.40574964735289</v>
+        <v>79.33461902601752</v>
       </c>
       <c r="AG96">
         <v>0.03427661582827568</v>
       </c>
       <c r="AH96">
-        <v>76.37147303152462</v>
+        <v>79.30034241018924</v>
       </c>
       <c r="AI96">
         <v>0.3641225964227157</v>
@@ -11965,16 +11965,16 @@
         <v>19.1169398104195</v>
       </c>
       <c r="R97">
-        <v>107.5488880411452</v>
+        <v>105.9018765483305</v>
       </c>
       <c r="S97">
         <v>0.03725765272974968</v>
       </c>
       <c r="T97">
-        <v>107.5116303884154</v>
+        <v>105.8646188956007</v>
       </c>
       <c r="U97">
-        <v>0.3966841256519371</v>
+        <v>0.3910211755550693</v>
       </c>
       <c r="V97">
         <v>0.3</v>
@@ -11983,7 +11983,7 @@
         <v>0</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>-1.647011492814686</v>
       </c>
       <c r="Y97">
         <v>124.7357046438279</v>
@@ -11995,7 +11995,7 @@
         <v>124.6994181705537</v>
       </c>
       <c r="AB97">
-        <v>0.3814007598572254</v>
+        <v>0.3747993887706261</v>
       </c>
       <c r="AC97">
         <v>0.3</v>
@@ -12007,13 +12007,13 @@
         <v>0</v>
       </c>
       <c r="AF97">
-        <v>68.23728260323928</v>
+        <v>71.20172647874436</v>
       </c>
       <c r="AG97">
         <v>0.03848487138748169</v>
       </c>
       <c r="AH97">
-        <v>68.1987977318518</v>
+        <v>71.16324160735688</v>
       </c>
       <c r="AI97">
         <v>0.3641225964227157</v>
